--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H405"/>
+  <dimension ref="A1:G408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -451,20 +451,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PREVIOUS</t>
+          <t>CONSENSUS</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CONSENSUS</t>
+          <t>FORECAST</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>FORECAST</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TIER</t>
         </is>
@@ -493,20 +488,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>2.4%</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="G2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -533,20 +523,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>84.7%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>85.0%</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="G3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -571,18 +556,13 @@
           <t>8.5%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>6.4%</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -607,18 +587,13 @@
           <t>6.6%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>6.8%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>5.5%</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -643,14 +618,9 @@
           <t>$6.81T</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>$6.81T</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -675,18 +645,13 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>3.7%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -711,14 +676,9 @@
           <t>3.5%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>11.4%</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -743,14 +703,9 @@
           <t>¥1752.9B</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>¥-1458.4B</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
+      <c r="G9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -775,14 +730,9 @@
           <t>¥-384.4B</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>¥-315.2B</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
+      <c r="G10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -807,18 +757,13 @@
           <t>0.5%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>0.8%</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="G11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -843,18 +788,13 @@
           <t>5.0%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>5.7%</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>3.1%</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="G12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -879,18 +819,13 @@
           <t>S$28.81B</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>S$33.89B</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
         <is>
           <t>S$ 36B</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="G13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -915,18 +850,13 @@
           <t>1.39%</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
         <is>
           <t>1.5%</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="G14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -943,22 +873,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.982%</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.876%</t>
-        </is>
-      </c>
+          <t>0.3098%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
+      <c r="G15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -975,22 +900,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.3098%</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.3110%</t>
-        </is>
-      </c>
+          <t>0.982%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
+      <c r="G16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1015,18 +935,13 @@
           <t>7.47%</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>8.89%</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>9.4%</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="G17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1051,18 +966,13 @@
           <t>-2.78%</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-3.79%</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>-3.5%</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="G18" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1089,20 +999,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="G19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1127,18 +1032,13 @@
           <t>2.51%</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2.14%</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="G20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1165,20 +1065,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
+      <c r="G21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1203,18 +1098,13 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
+      <c r="G22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1239,14 +1129,9 @@
           <t>2.570%</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2.570%</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
+      <c r="G23" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1263,30 +1148,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1303,30 +1183,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1343,30 +1218,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1383,30 +1253,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1423,7 +1288,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1433,20 +1298,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1463,31 +1323,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CNY2860B</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>CNY6200.0B</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>3</v>
+          <t>CNY1000.0B</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1503,30 +1358,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>7.2%</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>7.5%</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>7.6%</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>7.3%</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
+      <c r="G30" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1543,31 +1393,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY990B</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY800B</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>CNY1000.0B</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>2</v>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1583,30 +1428,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.2%</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
+          <t>CNY6200.0B</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1631,18 +1471,13 @@
           <t>$180.7B</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>$147.6B</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
         <is>
           <t>$ 100B</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="G33" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1659,7 +1494,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Employment Change QoQ PrelQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1669,20 +1504,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1699,30 +1529,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Employment Change YoY PrelQ4</t>
+          <t>GDP Growth Rate YoY 2nd EstQ4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1739,7 +1564,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Employment Change QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1749,20 +1574,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1779,30 +1599,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY 2nd EstQ4</t>
+          <t>Employment Change YoY PrelQ4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
+          <t>1.1%</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1837,12 +1652,7 @@
           <t>21%</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1867,14 +1677,9 @@
           <t>11.4%</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>11.5%</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1899,14 +1704,9 @@
           <t>10.3%</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>10.8%</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1931,14 +1731,9 @@
           <t>$638.26B</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>$630.61B</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="n">
+      <c r="G41" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1961,8 +1756,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
+      <c r="G42" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1974,32 +1768,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>161.5K</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>153K</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>3</v>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2015,26 +1808,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2051,26 +1839,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2087,31 +1870,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>2</v>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -2137,20 +1911,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="G47" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2162,35 +1931,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2217,7 +1977,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2225,12 +1985,7 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
+      <c r="G49" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2257,20 +2012,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="G50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2297,7 +2047,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2305,12 +2055,7 @@
           <t>0.2%</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
+      <c r="G51" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2322,31 +2067,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>153K</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2358,12 +2098,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2373,21 +2113,16 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>2</v>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -2403,27 +2138,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>3</v>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2439,27 +2173,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>3</v>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2475,30 +2208,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
+          <t>77.4%</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2515,31 +2243,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>2</v>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2555,30 +2274,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>77.7%</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>77.4%</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2595,26 +2309,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2641,20 +2350,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="G60" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2681,7 +2385,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2689,12 +2393,7 @@
           <t>0.2%</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
+      <c r="G61" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2717,8 +2416,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
+      <c r="G62" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2735,30 +2433,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
+          <t>9.9%</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2775,30 +2468,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>9.9%</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2823,14 +2511,9 @@
           <t>481</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="n">
+      <c r="G65" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2855,14 +2538,9 @@
           <t>588</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="n">
+      <c r="G66" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2885,8 +2563,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="n">
+      <c r="G67" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2898,27 +2575,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2933,26 +2605,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2962,27 +2629,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>12.0%</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2997,26 +2663,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3031,27 +2688,18 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>1</v>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -3067,27 +2715,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>2</v>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -3103,26 +2746,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3139,27 +2777,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>3</v>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -3175,23 +2808,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>3</v>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3207,26 +2839,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3249,20 +2876,15 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
           <t>1.1%</t>
         </is>
       </c>
-      <c r="H78" t="n">
+      <c r="G78" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3285,20 +2907,15 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-2.5%</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
           <t>4.8%</t>
         </is>
       </c>
-      <c r="H79" t="n">
+      <c r="G79" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3319,18 +2936,13 @@
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>$3.85B</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
         <is>
           <t>$4.5B</t>
         </is>
       </c>
-      <c r="H80" t="n">
+      <c r="G80" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3353,20 +2965,15 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>$2.24B</t>
+          <t>$1.91B</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
           <t>$2.2B</t>
         </is>
       </c>
-      <c r="H81" t="n">
+      <c r="G81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3389,16 +2996,11 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>4.78%</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
           <t>6.99%</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="n">
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3421,16 +3023,11 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>11.07%</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
           <t>9.95%</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="n">
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3451,18 +3048,13 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="H84" t="n">
+      <c r="G84" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3485,7 +3077,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3493,12 +3085,7 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
+      <c r="G85" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3519,18 +3106,13 @@
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-2.7%</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
         <is>
           <t>-1.6%</t>
         </is>
       </c>
-      <c r="H86" t="n">
+      <c r="G86" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3553,20 +3135,15 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="H87" t="n">
+      <c r="G87" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3587,14 +3164,9 @@
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2.840%</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
+      <c r="G88" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3617,20 +3189,15 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>€4.218B</t>
+          <t>€4.35B</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>€4.35B</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
           <t>€4.5B</t>
         </is>
       </c>
-      <c r="H89" t="n">
+      <c r="G89" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3651,18 +3218,13 @@
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>€-5.13B</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
         <is>
           <t>€ -4.9B</t>
         </is>
       </c>
-      <c r="H90" t="n">
+      <c r="G90" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3683,18 +3245,13 @@
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>€16.4B</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
         <is>
           <t>€ 33B</t>
         </is>
       </c>
-      <c r="H91" t="n">
+      <c r="G91" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3715,14 +3272,9 @@
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2.4019%</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="n">
+      <c r="G92" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3745,8 +3297,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="n">
+      <c r="G93" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3767,18 +3318,13 @@
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H94" t="n">
+      <c r="G94" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3801,20 +3347,15 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>231.5K</t>
+          <t>250K</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>250K</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
           <t>220.0K</t>
         </is>
       </c>
-      <c r="H95" t="n">
+      <c r="G95" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3837,16 +3378,11 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>C$16.4B</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
           <t>C$14.23B</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="n">
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3867,14 +3403,9 @@
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>C$17.85B</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="n">
+      <c r="G97" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3895,14 +3426,9 @@
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2.224%</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="n">
+      <c r="G98" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3923,14 +3449,9 @@
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>2.450%</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="n">
+      <c r="G99" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3951,14 +3472,9 @@
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2.358%</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="n">
+      <c r="G100" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3981,8 +3497,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="n">
+      <c r="G101" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3994,19 +3509,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="n">
+      <c r="G102" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4018,19 +3532,18 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="n">
+      <c r="G103" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4042,23 +3555,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>$59.95B</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="n">
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4070,23 +3582,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>$38.01B</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="n">
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4098,27 +3609,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>$-21.94B</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>$-24.0B</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>TRY-150.0B</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4130,19 +3636,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="n">
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4154,27 +3663,18 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>7.3%</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
+      <c r="G108" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4186,27 +3686,18 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
+      <c r="G109" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4218,19 +3709,18 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="n">
+      <c r="G110" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4242,27 +3732,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>TRY-829.2B</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>TRY-150.0B</t>
-        </is>
-      </c>
-      <c r="H111" t="n">
+      <c r="G111" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4285,8 +3766,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="n">
+      <c r="G112" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4309,8 +3789,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="n">
+      <c r="G113" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4333,7 +3812,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4341,12 +3820,7 @@
           <t>4.1%</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
+      <c r="G114" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4367,14 +3841,9 @@
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>1.983%</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
+      <c r="G115" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4397,8 +3866,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
+      <c r="G116" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4419,14 +3887,9 @@
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>2.99%</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="n">
+      <c r="G117" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4447,14 +3910,9 @@
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>2.98%</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
+      <c r="G118" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4471,27 +3929,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Claimant Count ChangeJAN</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="H119" t="n">
-        <v>1</v>
+          <t>7.0K</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -4507,27 +3960,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>5.9%</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
-      <c r="H120" t="n">
-        <v>2</v>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -4543,22 +3991,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Employment ChangeDEC</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>36K</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-130K</t>
-        </is>
-      </c>
-      <c r="H121" t="n">
+          <t>5.9%</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4575,23 +4022,18 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>Employment ChangeDEC</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>5.6%</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
-        <v>3</v>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-130K</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -4607,22 +4049,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-47K</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-55.0K</t>
-        </is>
-      </c>
-      <c r="H123" t="n">
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4639,26 +4076,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Claimant Count ChangeJAN</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>0.7K</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>7.0K</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
+          <t>-55.0K</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4675,27 +4103,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
-        <v>2</v>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -4711,27 +4134,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
-        <v>2</v>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -4747,27 +4165,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="H127" t="n">
-        <v>3</v>
+          <t>1.4%</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -4783,27 +4196,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="H128" t="n">
-        <v>3</v>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -4814,32 +4222,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
-        <v>3</v>
+          <t>32.4%</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -4850,23 +4249,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>8.1M</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4889,8 +4287,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="n">
+      <c r="G131" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4902,27 +4299,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>8.011M</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>8.1M</t>
-        </is>
-      </c>
-      <c r="H132" t="n">
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4934,28 +4330,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>32.1%</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>32.4%</t>
-        </is>
-      </c>
-      <c r="H133" t="n">
-        <v>2</v>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4975,18 +4366,13 @@
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H134" t="n">
+      <c r="G134" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5009,20 +4395,15 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H135" t="n">
+      <c r="G135" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5045,7 +4426,7 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-90.4</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5053,12 +4434,7 @@
           <t>-89</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-89</t>
-        </is>
-      </c>
-      <c r="H136" t="n">
+      <c r="G136" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5081,8 +4457,7 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="n">
+      <c r="G137" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5103,14 +4478,9 @@
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="n">
+      <c r="G138" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5133,20 +4503,15 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-12.6</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H139" t="n">
+      <c r="G139" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5169,20 +4534,15 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
+      <c r="G140" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5213,12 +4573,7 @@
           <t>2.4%</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="H141" t="n">
+      <c r="G141" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5239,18 +4594,13 @@
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
         <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="H142" t="n">
+      <c r="G142" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5267,23 +4617,18 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
         <is>
           <t>1.8%</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>2</v>
+      <c r="G143" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -5299,23 +4644,18 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>1</v>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -5337,20 +4677,15 @@
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H145" t="n">
+      <c r="G145" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5373,8 +4708,7 @@
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="n">
+      <c r="G146" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5402,15 +4736,10 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="H147" t="n">
+      <c r="G147" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5433,8 +4762,7 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="n">
+      <c r="G148" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5457,8 +4785,7 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="n">
+      <c r="G149" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5479,14 +4806,9 @@
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>4.225%</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="n">
+      <c r="G150" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5507,14 +4829,9 @@
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>4.185%</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="n">
+      <c r="G151" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5537,8 +4854,7 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="n">
+      <c r="G152" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5555,19 +4871,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>4.025%</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="n">
-        <v>3</v>
+      <c r="G153" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -5578,19 +4889,18 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="n">
+      <c r="G154" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5602,20 +4912,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="n">
-        <v>2</v>
+      <c r="G155" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="156">
@@ -5635,18 +4944,13 @@
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>$1666M</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr">
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
         <is>
           <t>$1500.0M</t>
         </is>
       </c>
-      <c r="H156" t="n">
+      <c r="G156" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5667,14 +4971,9 @@
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>$79B</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="n">
+      <c r="G157" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5695,14 +4994,9 @@
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="n">
+      <c r="G158" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5723,14 +5017,9 @@
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="n">
+      <c r="G159" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5753,20 +5042,15 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>9.7%</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
           <t>2.0%</t>
         </is>
       </c>
-      <c r="H160" t="n">
+      <c r="G160" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5783,26 +5067,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>7.6%</t>
-        </is>
-      </c>
-      <c r="H161" t="n">
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5819,26 +5098,21 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5861,20 +5135,15 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>¥130.9B</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
           <t>¥-1400.0B</t>
         </is>
       </c>
-      <c r="H163" t="n">
+      <c r="G163" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5897,20 +5166,15 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
           <t>3.0%</t>
         </is>
       </c>
-      <c r="H164" t="n">
+      <c r="G164" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5931,18 +5195,13 @@
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr">
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H165" t="n">
+      <c r="G165" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5965,8 +5224,7 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="n">
+      <c r="G166" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5994,15 +5252,10 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="H167" t="n">
+      <c r="G167" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6025,20 +5278,15 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
           <t>3.3%</t>
         </is>
       </c>
-      <c r="H168" t="n">
+      <c r="G168" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6059,18 +5307,13 @@
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>-5.3%</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr">
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
         <is>
           <t>-5.0%</t>
         </is>
       </c>
-      <c r="H169" t="n">
+      <c r="G169" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6091,14 +5334,9 @@
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>0.5429%</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="n">
+      <c r="G170" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6115,26 +5353,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H171" t="n">
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6151,22 +5380,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H172" t="n">
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6183,22 +5411,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>-1.5%</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H173" t="n">
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6215,26 +5438,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="H174" t="n">
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6251,22 +5465,21 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H175" t="n">
+      <c r="G175" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6287,18 +5500,13 @@
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr">
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
         <is>
           <t>1.3%</t>
         </is>
       </c>
-      <c r="H176" t="n">
+      <c r="G176" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6321,20 +5529,15 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="H177" t="n">
+      <c r="G177" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6355,18 +5558,13 @@
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
         <is>
           <t>-0.7%</t>
         </is>
       </c>
-      <c r="H178" t="n">
+      <c r="G178" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6387,18 +5585,13 @@
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr">
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
         <is>
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="H179" t="n">
+      <c r="G179" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6421,20 +5614,15 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="H180" t="n">
+      <c r="G180" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6457,20 +5645,15 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
           <t>2.7%</t>
         </is>
       </c>
-      <c r="H181" t="n">
+      <c r="G181" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6491,18 +5674,13 @@
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr">
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H182" t="n">
+      <c r="G182" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6523,18 +5701,13 @@
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>10.39%</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
         <is>
           <t>10.5%</t>
         </is>
       </c>
-      <c r="H183" t="n">
+      <c r="G183" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6565,12 +5738,7 @@
           <t>5.75%</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>5.75%</t>
-        </is>
-      </c>
-      <c r="H184" t="n">
+      <c r="G184" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6601,12 +5769,7 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="H185" t="n">
+      <c r="G185" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6637,12 +5800,7 @@
           <t>6.5%</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>6.5%</t>
-        </is>
-      </c>
-      <c r="H186" t="n">
+      <c r="G186" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6659,22 +5817,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="H187" t="n">
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6695,18 +5848,13 @@
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr">
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
         <is>
           <t>3.6%</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="H188" t="n">
+      <c r="G188" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6727,18 +5875,13 @@
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="H189" t="n">
+      <c r="G189" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6750,20 +5893,23 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="n">
-        <v>3</v>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -6774,28 +5920,19 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="H191" t="n">
-        <v>2</v>
+      <c r="G191" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="192">
@@ -6815,18 +5952,13 @@
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>€34.6B</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
         <is>
           <t>€32B</t>
         </is>
       </c>
-      <c r="H192" t="n">
+      <c r="G192" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6849,7 +5981,7 @@
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>€27B</t>
+          <t>€30B</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6857,12 +5989,7 @@
           <t>€30B</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>€30B</t>
-        </is>
-      </c>
-      <c r="H193" t="n">
+      <c r="G193" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6883,18 +6010,13 @@
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>€-332M</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
         <is>
           <t>€ 3780M</t>
         </is>
       </c>
-      <c r="H194" t="n">
+      <c r="G194" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6915,14 +6037,9 @@
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>4.384%</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="n">
+      <c r="G195" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6943,14 +6060,9 @@
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>2.54%</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="n">
+      <c r="G196" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6967,22 +6079,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="H197" t="n">
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6999,22 +6106,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="H198" t="n">
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7031,18 +6133,13 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>2.487%</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="n">
+      <c r="G199" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7059,18 +6156,13 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>2.350%</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="n">
+      <c r="G200" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7091,14 +6183,9 @@
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>9.6%</t>
-        </is>
-      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="n">
+      <c r="G201" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7115,18 +6202,13 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>640.6</t>
-        </is>
-      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="n">
+      <c r="G202" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7143,18 +6225,13 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="n">
+      <c r="G203" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7171,18 +6248,13 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>230.0</t>
-        </is>
-      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="n">
+      <c r="G204" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7199,19 +6271,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="n">
-        <v>3</v>
+      <c r="G205" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -7227,19 +6294,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>6.95%</t>
-        </is>
-      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="n">
-        <v>2</v>
+      <c r="G206" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -7261,20 +6323,15 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>1.45M</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
           <t>1.47M</t>
         </is>
       </c>
-      <c r="H207" t="n">
+      <c r="G207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7297,20 +6354,15 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1.499M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>1.39M</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
           <t>1.35M</t>
         </is>
       </c>
-      <c r="H208" t="n">
+      <c r="G208" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7331,18 +6383,13 @@
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr">
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
         <is>
           <t>-0.8%</t>
         </is>
       </c>
-      <c r="H209" t="n">
+      <c r="G209" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7363,18 +6410,13 @@
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr">
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
         <is>
           <t>-9.0%</t>
         </is>
       </c>
-      <c r="H210" t="n">
+      <c r="G210" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7395,14 +6437,9 @@
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>5.3%</t>
-        </is>
-      </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="n">
+      <c r="G211" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7423,14 +6460,13 @@
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>$50 million</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="n">
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7451,18 +6487,13 @@
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr">
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
         <is>
           <t>0.6%</t>
         </is>
       </c>
-      <c r="H213" t="n">
+      <c r="G213" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7483,18 +6514,13 @@
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr">
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
         <is>
           <t>8.2%</t>
         </is>
       </c>
-      <c r="H214" t="n">
+      <c r="G214" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7515,14 +6541,9 @@
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>4.230%</t>
-        </is>
-      </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="n">
+      <c r="G215" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7543,18 +6564,13 @@
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr">
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
         <is>
           <t>48.8</t>
         </is>
       </c>
-      <c r="H216" t="n">
+      <c r="G216" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7575,14 +6591,9 @@
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>4.900%</t>
-        </is>
-      </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="n">
+      <c r="G217" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7605,8 +6616,7 @@
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="n">
+      <c r="G218" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7627,18 +6637,13 @@
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr">
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
         <is>
           <t>85.5</t>
         </is>
       </c>
-      <c r="H219" t="n">
+      <c r="G219" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7659,18 +6664,13 @@
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>2.45%</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
         <is>
           <t>1.5%</t>
         </is>
       </c>
-      <c r="H220" t="n">
+      <c r="G220" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7693,8 +6693,7 @@
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="n">
+      <c r="G221" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7711,23 +6710,18 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>91.2</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H222" t="n">
-        <v>2</v>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="223">
@@ -7743,23 +6737,18 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H223" t="n">
-        <v>3</v>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -7779,18 +6768,13 @@
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr">
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
         <is>
           <t>1.8%</t>
         </is>
       </c>
-      <c r="H224" t="n">
+      <c r="G224" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7811,14 +6795,9 @@
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>9.043M</t>
-        </is>
-      </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="n">
+      <c r="G225" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7841,8 +6820,7 @@
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="n">
+      <c r="G226" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7859,18 +6837,13 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Stock Investment by ForeignersFEB/15</t>
+          <t>Foreign Bond InvestmentFEB/15</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>¥-384.4B</t>
-        </is>
-      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="n">
+      <c r="G227" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7887,18 +6860,13 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentFEB/15</t>
+          <t>Stock Investment by ForeignersFEB/15</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>¥1752.9B</t>
-        </is>
-      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="n">
+      <c r="G228" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7921,20 +6889,15 @@
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="H229" t="n">
+      <c r="G229" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7957,20 +6920,15 @@
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>56.3K</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>20K</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
           <t>23.0K</t>
         </is>
       </c>
-      <c r="H230" t="n">
+      <c r="G230" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7991,18 +6949,13 @@
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>-23.7K</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr">
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
         <is>
           <t>33.0K</t>
         </is>
       </c>
-      <c r="H231" t="n">
+      <c r="G231" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8023,18 +6976,13 @@
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>80K</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr">
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
         <is>
           <t>-10.0K</t>
         </is>
       </c>
-      <c r="H232" t="n">
+      <c r="G232" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8062,15 +7010,10 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>67.1%</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
           <t>67.0%</t>
         </is>
       </c>
-      <c r="H233" t="n">
+      <c r="G233" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8091,18 +7034,13 @@
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
         <is>
           <t>3.1%</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="H234" t="n">
+      <c r="G234" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8123,18 +7061,13 @@
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
         <is>
           <t>3.6%</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="H235" t="n">
+      <c r="G235" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8151,18 +7084,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="n">
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8179,22 +7111,13 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>$-2.2B</t>
-        </is>
-      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
-      <c r="H237" t="n">
+      <c r="G237" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8215,18 +7138,13 @@
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr">
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="H238" t="n">
+      <c r="G238" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8249,20 +7167,15 @@
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="H239" t="n">
+      <c r="G239" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8283,18 +7196,13 @@
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr">
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
         <is>
           <t>1.1%</t>
         </is>
       </c>
-      <c r="H240" t="n">
+      <c r="G240" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8315,18 +7223,13 @@
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr">
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
         <is>
           <t>3.2%</t>
         </is>
       </c>
-      <c r="H241" t="n">
+      <c r="G241" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8347,14 +7250,9 @@
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>2.388%</t>
-        </is>
-      </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="n">
+      <c r="G242" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8375,14 +7273,9 @@
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>2.763%</t>
-        </is>
-      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="n">
+      <c r="G243" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8403,14 +7296,9 @@
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="n">
+      <c r="G244" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8427,18 +7315,13 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>3-Year OAT Auction</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>2.84%</t>
-        </is>
-      </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="n">
+      <c r="G245" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8450,23 +7333,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>3-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>2.51%</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="n">
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8478,27 +7360,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="H247" t="n">
+      <c r="G247" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8519,14 +7392,9 @@
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>2.74%</t>
-        </is>
-      </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="n">
+      <c r="G248" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8538,27 +7406,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
-      <c r="H249" t="n">
+      <c r="G249" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8570,20 +7429,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="n">
-        <v>3</v>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -8605,8 +7471,7 @@
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="n">
+      <c r="G251" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8618,32 +7483,23 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>-34</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
-      <c r="H252" t="n">
-        <v>2</v>
+          <t>18.0%</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -8663,14 +7519,9 @@
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="n">
+      <c r="G253" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8693,8 +7544,7 @@
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="n">
+      <c r="G254" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8715,14 +7565,9 @@
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>$96.93B</t>
-        </is>
-      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="n">
+      <c r="G255" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8743,18 +7588,13 @@
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr">
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
         <is>
           <t>-0.4%</t>
         </is>
       </c>
-      <c r="H256" t="n">
+      <c r="G256" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8775,18 +7615,13 @@
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr">
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="H257" t="n">
+      <c r="G257" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8807,14 +7642,9 @@
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="n">
+      <c r="G258" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8835,14 +7665,9 @@
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="n">
+      <c r="G259" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8863,14 +7688,9 @@
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>11.9</t>
-        </is>
-      </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="n">
+      <c r="G260" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8891,14 +7711,9 @@
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="n">
+      <c r="G261" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8919,14 +7734,9 @@
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>46.3</t>
-        </is>
-      </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="n">
+      <c r="G262" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8947,18 +7757,13 @@
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr">
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
         <is>
           <t>219.0K</t>
         </is>
       </c>
-      <c r="H263" t="n">
+      <c r="G263" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8979,18 +7784,13 @@
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>1850K</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr">
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
         <is>
           <t>1879.0K</t>
         </is>
       </c>
-      <c r="H264" t="n">
+      <c r="G264" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9013,20 +7813,15 @@
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H265" t="n">
+      <c r="G265" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9049,20 +7844,15 @@
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
           <t>220.0K</t>
         </is>
       </c>
-      <c r="H266" t="n">
+      <c r="G266" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9083,18 +7873,13 @@
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>9.1%</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr">
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
         <is>
           <t>10.0%</t>
         </is>
       </c>
-      <c r="H267" t="n">
+      <c r="G267" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9115,18 +7900,13 @@
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr">
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
         <is>
           <t>-0.2%</t>
         </is>
       </c>
-      <c r="H268" t="n">
+      <c r="G268" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9147,18 +7927,13 @@
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr">
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
         <is>
           <t>4.3%</t>
         </is>
       </c>
-      <c r="H269" t="n">
+      <c r="G269" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9179,18 +7954,13 @@
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr">
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="H270" t="n">
+      <c r="G270" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9211,18 +7981,13 @@
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr">
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H271" t="n">
+      <c r="G271" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9243,18 +8008,13 @@
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr">
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H272" t="n">
+      <c r="G272" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9275,18 +8035,13 @@
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr">
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="H273" t="n">
+      <c r="G273" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9309,8 +8064,7 @@
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="n">
+      <c r="G274" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9333,7 +8087,7 @@
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -9341,12 +8095,7 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
+      <c r="G275" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9369,20 +8118,15 @@
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>-14.2</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
           <t>-14.4</t>
         </is>
       </c>
-      <c r="H276" t="n">
+      <c r="G276" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9405,8 +8149,7 @@
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="n">
+      <c r="G277" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9427,14 +8170,9 @@
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>-100Bcf</t>
-        </is>
-      </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="n">
+      <c r="G278" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9457,8 +8195,7 @@
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="n">
+      <c r="G279" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9479,14 +8216,9 @@
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>4.250%</t>
-        </is>
-      </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="n">
+      <c r="G280" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9507,14 +8239,9 @@
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>4.240%</t>
-        </is>
-      </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="n">
+      <c r="G281" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9535,14 +8262,9 @@
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>0.18M</t>
-        </is>
-      </c>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="n">
+      <c r="G282" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9563,14 +8285,9 @@
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>0.082M</t>
-        </is>
-      </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="n">
+      <c r="G283" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9591,14 +8308,9 @@
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>0.159M</t>
-        </is>
-      </c>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="n">
+      <c r="G284" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9619,14 +8331,9 @@
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>0.135M</t>
-        </is>
-      </c>
+      <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="n">
+      <c r="G285" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9643,18 +8350,13 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>-0.009M</t>
-        </is>
-      </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="n">
+      <c r="G286" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9671,18 +8373,13 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>0.872M</t>
-        </is>
-      </c>
+      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="n">
+      <c r="G287" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9699,18 +8396,13 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>-0.184M</t>
-        </is>
-      </c>
+      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
-      <c r="H288" t="n">
+      <c r="G288" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9727,18 +8419,13 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>6.87%</t>
-        </is>
-      </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="n">
+      <c r="G289" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9755,19 +8442,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>6.09%</t>
-        </is>
-      </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="n">
-        <v>3</v>
+      <c r="G290" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -9783,18 +8465,13 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="n">
+      <c r="G291" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9806,24 +8483,19 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>2-Year Bond Auction</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>4.07M</t>
-        </is>
-      </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="n">
-        <v>2</v>
+      <c r="G292" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -9834,23 +8506,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2-Year Bond Auction</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>2.589%</t>
-        </is>
-      </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="n">
+      <c r="G293" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9873,8 +8540,7 @@
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="n">
+      <c r="G294" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9886,23 +8552,18 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>14.62%</t>
-        </is>
-      </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="n">
+      <c r="G295" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9914,23 +8575,22 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>15.031%</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="n">
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9951,14 +8611,9 @@
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>15.035%</t>
-        </is>
-      </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="n">
+      <c r="G297" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9970,23 +8625,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>2.055%</t>
-        </is>
-      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="n">
+      <c r="G298" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9998,27 +8648,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>TRY9.251T</t>
-        </is>
-      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
-      <c r="H299" t="n">
+      <c r="G299" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10041,8 +8682,7 @@
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="n">
+      <c r="G300" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10063,18 +8703,13 @@
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr">
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="H301" t="n">
+      <c r="G301" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10095,14 +8730,9 @@
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>$6.81T</t>
-        </is>
-      </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="n">
+      <c r="G302" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10114,20 +8744,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="n">
-        <v>2</v>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -10147,18 +8780,13 @@
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr">
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
         <is>
           <t>51.3</t>
         </is>
       </c>
-      <c r="H304" t="n">
+      <c r="G304" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10170,28 +8798,19 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
-      <c r="H305" t="n">
-        <v>3</v>
+      <c r="G305" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -10211,18 +8830,13 @@
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr">
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="H306" t="n">
+      <c r="G306" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10243,18 +8857,13 @@
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr">
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H307" t="n">
+      <c r="G307" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10275,18 +8884,13 @@
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr">
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
         <is>
           <t>3.7%</t>
         </is>
       </c>
-      <c r="H308" t="n">
+      <c r="G308" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10309,20 +8913,15 @@
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
           <t>3.2%</t>
         </is>
       </c>
-      <c r="H309" t="n">
+      <c r="G309" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10343,18 +8942,13 @@
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr">
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
         <is>
           <t>2.6%</t>
         </is>
       </c>
-      <c r="H310" t="n">
+      <c r="G310" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10375,18 +8969,13 @@
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr">
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H311" t="n">
+      <c r="G311" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10414,15 +9003,10 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>-22</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="H312" t="n">
+      <c r="G312" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10439,23 +9023,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr"/>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="H313" t="n">
-        <v>3</v>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>49.6</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -10471,26 +9054,17 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="H314" t="n">
+          <t>52.2</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10507,23 +9081,18 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>52.2</t>
-        </is>
-      </c>
-      <c r="H315" t="n">
-        <v>2</v>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -10543,14 +9112,9 @@
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>0.3098%</t>
-        </is>
-      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="n">
+      <c r="G316" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10567,22 +9131,17 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="H317" t="n">
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10603,18 +9162,13 @@
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr">
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="H318" t="n">
+      <c r="G318" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10631,22 +9185,17 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HSBC Services PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="H319" t="n">
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10663,27 +9212,18 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H320" t="n">
-        <v>1</v>
+      <c r="G320" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -10699,23 +9239,18 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr"/>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
-      <c r="H321" t="n">
-        <v>2</v>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -10737,20 +9272,15 @@
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>£-17.81B</t>
+          <t>£20.5B</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
           <t>£19.0B</t>
         </is>
       </c>
-      <c r="H322" t="n">
+      <c r="G322" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10767,23 +9297,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr">
-        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="H323" t="n">
-        <v>3</v>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -10799,23 +9328,18 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="H324" t="n">
-        <v>3</v>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="325">
@@ -10831,23 +9355,18 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr"/>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="H325" t="n">
-        <v>3</v>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -10863,23 +9382,18 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H326" t="n">
-        <v>2</v>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -10901,8 +9415,7 @@
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="n">
+      <c r="G327" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10925,20 +9438,15 @@
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
           <t>45.4</t>
         </is>
       </c>
-      <c r="H328" t="n">
+      <c r="G328" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10955,26 +9463,17 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H329" t="n">
+          <t>47.2</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10991,22 +9490,21 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
-      </c>
-      <c r="H330" t="n">
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G330" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11023,27 +9521,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>45.5</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>45.1</t>
-        </is>
-      </c>
-      <c r="H331" t="n">
-        <v>1</v>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -11063,18 +9556,13 @@
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>50.5</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr">
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
         <is>
           <t>50.1</t>
         </is>
       </c>
-      <c r="H332" t="n">
+      <c r="G332" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11091,27 +9579,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="H333" t="n">
-        <v>2</v>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -11122,28 +9605,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H334" t="n">
-        <v>2</v>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -11154,31 +9636,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>46.8</t>
-        </is>
-      </c>
-      <c r="H335" t="n">
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11190,32 +9667,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="H336" t="n">
-        <v>2</v>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="337">
@@ -11237,7 +9709,7 @@
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -11245,12 +9717,7 @@
           <t>0.6%</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="H337" t="n">
+      <c r="G337" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11262,31 +9729,26 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="H338" t="n">
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11298,32 +9760,27 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="H339" t="n">
-        <v>3</v>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="340">
@@ -11334,32 +9791,23 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="H340" t="n">
-        <v>3</v>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -11375,26 +9823,21 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H341" t="n">
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11411,23 +9854,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>50.6</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr">
-        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H342" t="n">
-        <v>3</v>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -11443,27 +9885,18 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>48.3</t>
-        </is>
-      </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="H343" t="n">
-        <v>1</v>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -11485,8 +9918,7 @@
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="n">
+      <c r="G344" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11507,14 +9939,9 @@
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>$638.26B</t>
-        </is>
-      </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
-      <c r="H345" t="n">
+      <c r="G345" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11531,27 +9958,18 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
+      <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="H346" t="n">
-        <v>2</v>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="347">
@@ -11573,7 +9991,7 @@
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -11581,12 +9999,7 @@
           <t>0.6%</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="H347" t="n">
+      <c r="G347" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11603,22 +10016,17 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="H348" t="n">
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11635,23 +10043,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="H349" t="n">
-        <v>3</v>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="350">
@@ -11673,20 +10080,15 @@
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="H350" t="n">
+      <c r="G350" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11709,7 +10111,7 @@
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -11717,12 +10119,7 @@
           <t>1.6%</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="H351" t="n">
+      <c r="G351" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11744,13 +10141,12 @@
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr">
+      <c r="F352" t="inlineStr">
         <is>
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="H352" t="n">
+      <c r="G352" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11771,18 +10167,13 @@
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr">
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="H353" t="n">
+      <c r="G353" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11805,8 +10196,7 @@
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
-      <c r="H354" t="n">
+      <c r="G354" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11823,22 +10213,17 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr"/>
-      <c r="G355" t="inlineStr">
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="H355" t="n">
+      <c r="G355" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11859,18 +10244,13 @@
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr">
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
         <is>
           <t>51.3</t>
         </is>
       </c>
-      <c r="H356" t="n">
+      <c r="G356" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11887,22 +10267,17 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr">
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="H357" t="n">
+      <c r="G357" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11919,27 +10294,22 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>4.17M</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>4.16M</t>
-        </is>
-      </c>
-      <c r="H358" t="n">
-        <v>1</v>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="359">
@@ -11955,23 +10325,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>-1.7%</t>
-        </is>
-      </c>
-      <c r="H359" t="n">
-        <v>2</v>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="360">
@@ -11987,27 +10356,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="H360" t="n">
-        <v>2</v>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="361">
@@ -12029,7 +10393,7 @@
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -12037,12 +10401,7 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="H361" t="n">
+      <c r="G361" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12059,27 +10418,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="H362" t="n">
-        <v>3</v>
+          <t>4.16M</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="363">
@@ -12095,27 +10449,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="H363" t="n">
-        <v>3</v>
+          <t>-1.7%</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -12131,27 +10476,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="H364" t="n">
-        <v>3</v>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -12173,8 +10513,7 @@
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="n">
+      <c r="G365" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12197,8 +10536,7 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="n">
+      <c r="G366" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12219,14 +10557,9 @@
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>BRL261.3B</t>
-        </is>
-      </c>
+      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="n">
+      <c r="G367" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12247,18 +10580,13 @@
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>-27.1%</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr">
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
         <is>
           <t>-18.0%</t>
         </is>
       </c>
-      <c r="H368" t="n">
+      <c r="G368" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12275,18 +10603,13 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
+      <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="n">
+      <c r="G369" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12303,18 +10626,13 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
-      <c r="H370" t="n">
+      <c r="G370" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12338,7 +10656,6 @@
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr"/>
-      <c r="H371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12357,18 +10674,13 @@
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr">
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
         <is>
           <t>2.0%</t>
         </is>
       </c>
-      <c r="H372" t="n">
+      <c r="G372" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12389,18 +10701,13 @@
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr">
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
         <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="H373" t="n">
+      <c r="G373" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12421,18 +10728,13 @@
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr">
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr">
         <is>
           <t>2.1%</t>
         </is>
       </c>
-      <c r="H374" t="n">
+      <c r="G374" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12453,14 +10755,9 @@
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>2.725%</t>
-        </is>
-      </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="n">
+      <c r="G375" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12477,19 +10774,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
-      </c>
+      <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="n">
-        <v>2</v>
+      <c r="G376" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -12505,19 +10797,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>74.6%</t>
-        </is>
-      </c>
+      <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="n">
-        <v>3</v>
+      <c r="G377" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="378">
@@ -12533,23 +10820,18 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>84.2</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="H378" t="n">
-        <v>3</v>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -12569,18 +10851,13 @@
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>86.1</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr">
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
         <is>
           <t>85.1</t>
         </is>
       </c>
-      <c r="H379" t="n">
+      <c r="G379" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12597,23 +10874,18 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>85.1</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H380" t="n">
-        <v>1</v>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -12635,7 +10907,7 @@
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -12643,12 +10915,7 @@
           <t>2.5%</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="H381" t="n">
+      <c r="G381" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12679,12 +10946,7 @@
           <t>2.7%</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="H382" t="n">
+      <c r="G382" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12707,7 +10969,7 @@
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>127.07</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -12715,12 +10977,7 @@
           <t>126.71</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>126.71</t>
-        </is>
-      </c>
-      <c r="H383" t="n">
+      <c r="G383" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12743,7 +11000,7 @@
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -12751,12 +11008,7 @@
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="H384" t="n">
+      <c r="G384" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12777,14 +11029,9 @@
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>2.576%</t>
-        </is>
-      </c>
+      <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
-      <c r="H385" t="n">
+      <c r="G385" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12805,14 +11052,9 @@
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>2.223%</t>
-        </is>
-      </c>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr"/>
-      <c r="H386" t="n">
+      <c r="G386" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12835,8 +11077,7 @@
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
-      <c r="H387" t="n">
+      <c r="G387" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12857,14 +11098,9 @@
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>86.2</t>
-        </is>
-      </c>
+      <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
-      <c r="H388" t="n">
+      <c r="G388" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12881,18 +11117,13 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
-      <c r="H389" t="n">
+      <c r="G389" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12909,18 +11140,13 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>3.69%</t>
-        </is>
-      </c>
+      <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
-      <c r="H390" t="n">
+      <c r="G390" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12937,18 +11163,13 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>3.72%</t>
-        </is>
-      </c>
+      <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
-      <c r="H391" t="n">
+      <c r="G391" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12965,18 +11186,13 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
+      <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr"/>
-      <c r="H392" t="n">
+      <c r="G392" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12999,8 +11215,7 @@
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
-      <c r="H393" t="n">
+      <c r="G393" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13021,14 +11236,9 @@
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
+      <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
-      <c r="H394" t="n">
+      <c r="G394" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13045,14 +11255,13 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr"/>
-      <c r="H395" t="n">
+      <c r="G395" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13069,14 +11278,13 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
-      <c r="H396" t="n">
+      <c r="G396" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13093,14 +11301,13 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
-      <c r="H397" t="n">
+      <c r="G397" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13121,14 +11328,9 @@
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
+      <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
-      <c r="H398" t="n">
+      <c r="G398" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13151,8 +11353,7 @@
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr"/>
-      <c r="H399" t="n">
+      <c r="G399" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13175,8 +11376,7 @@
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr"/>
-      <c r="H400" t="n">
+      <c r="G400" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13199,8 +11399,7 @@
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr"/>
-      <c r="H401" t="n">
+      <c r="G401" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13221,18 +11420,13 @@
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr">
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
         <is>
           <t>2.75%</t>
         </is>
       </c>
-      <c r="H402" t="n">
+      <c r="G402" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13255,8 +11449,7 @@
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr"/>
-      <c r="H403" t="n">
+      <c r="G403" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13279,8 +11472,7 @@
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr"/>
-      <c r="H404" t="n">
+      <c r="G404" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13301,14 +11493,90 @@
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>2.770%</t>
-        </is>
-      </c>
+      <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
-      <c r="H405" t="n">
+      <c r="G405" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2025-02-25 11:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>SAR 34B</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2025-02-25 11:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>SAR 94.5B</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2025-02-25 11:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>ImportsDEC</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>SAR 60.5B</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1393,26 +1393,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1428,22 +1428,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1768,23 +1768,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1804,18 +1804,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1830,23 +1830,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1866,26 +1870,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1901,12 +1905,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1916,7 +1920,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1936,22 +1940,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2006,26 +2006,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2036,27 +2036,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2076,22 +2072,26 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2117,16 +2117,16 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -2173,18 +2173,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2239,26 +2239,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2274,22 +2270,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2309,22 +2305,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2959,22 +2959,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>9.95%</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2990,18 +2986,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>6.99%</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3017,13 +3017,13 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G412"/>
+  <dimension ref="A1:G415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,26 +1323,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1428,26 +1428,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1773,22 +1773,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1799,12 +1803,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1814,16 +1818,16 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -1834,23 +1838,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1870,26 +1878,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1905,12 +1913,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1920,7 +1928,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1940,18 +1948,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -1971,12 +1979,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2006,26 +2014,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2036,27 +2044,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2076,22 +2080,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2106,23 +2106,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2173,26 +2173,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2208,22 +2204,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2243,22 +2239,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2274,22 +2274,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2309,18 +2309,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6344,18 +6344,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -6371,22 +6375,18 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6402,18 +6402,18 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -6883,18 +6883,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>67.1%</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -6914,18 +6910,18 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
@@ -6941,18 +6937,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>67.1%</t>
+        </is>
+      </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>3-Year OAT Auction</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -7333,21 +7333,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
         <v>3</v>
       </c>
@@ -7365,7 +7361,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>3-Year OAT Auction</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7383,17 +7379,21 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G248" t="n">
         <v>3</v>
       </c>
@@ -7406,21 +7406,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
+      <c r="F249" t="inlineStr"/>
       <c r="G249" t="n">
         <v>3</v>
       </c>
@@ -7438,7 +7434,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -7479,27 +7475,19 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7510,17 +7498,21 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
       <c r="G253" t="n">
         <v>3</v>
       </c>
@@ -7533,19 +7525,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -7584,14 +7584,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7611,14 +7611,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -7702,19 +7702,23 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G261" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -7730,7 +7734,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -7780,16 +7784,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
         <v>3</v>
       </c>
@@ -7807,22 +7807,18 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266">
@@ -7860,23 +7856,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -7892,18 +7892,18 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -7919,14 +7919,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -7946,18 +7946,18 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8004,14 +8004,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8744,23 +8744,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -8825,19 +8821,23 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -8880,18 +8880,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -8907,14 +8907,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -8965,18 +8965,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -9239,18 +9239,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9270,14 +9266,18 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9521,22 +9521,18 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
-      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -9552,18 +9548,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -9610,22 +9610,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -9641,18 +9641,18 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -9672,22 +9672,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -9958,14 +9958,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -9985,14 +9985,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10240,14 +10240,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -10267,14 +10267,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -10294,18 +10294,18 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -10325,18 +10325,18 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -10356,18 +10356,18 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -10387,18 +10387,18 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -10418,18 +10418,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G362" t="n">
@@ -10449,18 +10445,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -10476,22 +10476,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -10571,17 +10571,21 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G368" t="n">
         <v>3</v>
       </c>
@@ -10594,21 +10598,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F369" t="inlineStr"/>
       <c r="G369" t="n">
         <v>3</v>
       </c>
@@ -10621,12 +10621,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10847,18 +10847,18 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -10874,18 +10874,18 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -10901,22 +10901,22 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -10963,18 +10963,18 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G383" t="n">
@@ -10994,22 +10994,22 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -11619,27 +11619,23 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -11650,17 +11646,25 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="G411" t="n">
         <v>2</v>
       </c>
@@ -11673,22 +11677,91 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2025-02-25 15:40:00+05:30</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2-Year BTP Short Term Auction</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2025-02-25 15:40:00+05:30</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>BTP€i Auction</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2025-02-25 15:40:00+05:30</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G415"/>
+  <dimension ref="A1:G418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,26 +1323,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1393,26 +1393,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1428,22 +1428,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1783,16 +1783,16 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1808,22 +1808,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1838,27 +1834,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1878,26 +1870,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1913,12 +1905,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1928,7 +1920,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1948,22 +1940,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1979,12 +1975,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1994,7 +1990,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2014,26 +2010,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2044,23 +2040,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2075,23 +2075,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2111,18 +2111,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2173,18 +2173,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2239,26 +2239,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2274,22 +2270,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2309,22 +2305,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2629,19 +2629,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2654,23 +2658,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2688,22 +2688,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2761,11 +2761,11 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2781,18 +2781,18 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -2812,14 +2812,18 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -2839,18 +2843,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -2870,18 +2870,18 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Non-Oil Exports MoMJAN</t>
+          <t>Non-Oil Exports YoYJAN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -2901,18 +2901,18 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Non-Oil Exports YoYJAN</t>
+          <t>Non-Oil Exports MoMJAN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -2959,18 +2959,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>9.95%</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2986,22 +2990,18 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>6.99%</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -3017,13 +3017,13 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>9.95%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3187,14 +3187,10 @@
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>€4.35B</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>€4.5B</t>
+          <t>€ -4.9B</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -3209,7 +3205,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3218,10 +3214,14 @@
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>€4.35B</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>€ -4.9B</t>
+          <t>€4.5B</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -3628,21 +3628,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>2</v>
       </c>
@@ -3687,14 +3683,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>TRY-150.0B</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -3709,17 +3705,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>TRY-150.0B</t>
+        </is>
+      </c>
       <c r="G110" t="n">
         <v>2</v>
       </c>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -4497,22 +4497,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -4590,14 +4590,18 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -4617,22 +4621,18 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -4894,14 +4894,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
@@ -4912,19 +4912,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
@@ -5036,22 +5036,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -5067,18 +5067,18 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5129,18 +5129,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5160,22 +5160,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -5353,14 +5353,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5380,14 +5384,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5407,14 +5411,18 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5434,18 +5442,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5496,14 +5500,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5523,18 +5527,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -5554,14 +5554,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5581,18 +5581,18 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5608,18 +5608,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5639,22 +5635,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -5670,18 +5666,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -6079,14 +6079,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -6106,14 +6106,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -6271,14 +6271,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -6294,14 +6294,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Annual Budget Speech</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -6632,17 +6632,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual Budget Speech</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6655,21 +6659,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
         <v>3</v>
       </c>
@@ -6883,18 +6883,18 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
@@ -6910,18 +6910,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>67.1%</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231">
@@ -6937,22 +6941,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -6968,22 +6972,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
@@ -6999,22 +7003,18 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>20K</t>
-        </is>
-      </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -7084,12 +7084,16 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G236" t="n">
         <v>3</v>
       </c>
@@ -7107,16 +7111,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
+      <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
         <v>3</v>
       </c>
@@ -7638,12 +7638,16 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G258" t="n">
         <v>3</v>
       </c>
@@ -7684,7 +7688,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -7702,23 +7706,19 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
       <c r="G261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -7757,14 +7757,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -7807,18 +7807,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
@@ -7834,18 +7838,18 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
@@ -7856,27 +7860,23 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
@@ -7892,14 +7892,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -7946,18 +7946,18 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -7977,18 +7977,18 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -8004,18 +8004,18 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -8598,17 +8598,21 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G297" t="n">
         <v>3</v>
       </c>
@@ -8621,12 +8625,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -8644,21 +8648,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
         <v>3</v>
       </c>
@@ -8744,17 +8744,21 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
       <c r="G303" t="n">
         <v>2</v>
       </c>
@@ -8772,14 +8776,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -8799,18 +8803,18 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8821,23 +8825,19 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -8880,18 +8880,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -8907,18 +8907,18 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -8934,22 +8934,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8965,18 +8961,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -9023,18 +9023,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9054,18 +9050,18 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -9081,18 +9077,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -9266,22 +9266,18 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323">
@@ -9297,22 +9293,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>£20.5B</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
@@ -9328,18 +9324,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -9432,14 +9432,18 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -9459,18 +9463,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -9490,18 +9490,18 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -9521,14 +9521,18 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -9548,22 +9552,18 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
-      </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -9579,22 +9579,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -9734,18 +9734,18 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -9765,14 +9765,18 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -9792,18 +9796,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -9958,14 +9958,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -9985,18 +9985,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -10012,22 +10016,18 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10240,14 +10240,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -10267,14 +10267,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -10325,18 +10325,18 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -10356,18 +10356,18 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -10387,22 +10387,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -10418,18 +10418,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -10476,18 +10480,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10665,21 +10665,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
+      <c r="F372" t="inlineStr"/>
       <c r="G372" t="n">
         <v>3</v>
       </c>
@@ -10697,14 +10693,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -10724,14 +10720,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -10746,17 +10742,21 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="G375" t="n">
         <v>3</v>
       </c>
@@ -10820,18 +10820,18 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -10874,18 +10874,18 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -11438,12 +11438,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>20-Year KTB Auction</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -11484,12 +11484,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>20-Year KTB Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -11619,23 +11619,19 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -11677,19 +11673,23 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -11765,6 +11765,83 @@
         <v>3</v>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2025-02-25 16:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Bund/g Auction</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2025-02-25 16:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>CBI Distributive TradesFEB</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-26</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2025-02-25 16:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G421"/>
+  <dimension ref="A1:G429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1428,26 +1428,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1768,23 +1768,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1804,18 +1804,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1830,27 +1830,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1870,26 +1866,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1905,12 +1901,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1920,7 +1916,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1940,22 +1936,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -1975,12 +1967,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1990,7 +1982,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2010,26 +2002,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2040,23 +2032,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2076,22 +2072,26 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2117,16 +2117,16 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -2173,26 +2173,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2208,22 +2204,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2243,22 +2239,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2274,22 +2274,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2309,18 +2309,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2575,19 +2575,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2600,23 +2604,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2634,18 +2634,18 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2688,22 +2688,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2750,22 +2750,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2781,22 +2777,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -2843,14 +2839,18 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -2870,18 +2870,18 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Non-Oil Exports MoMJAN</t>
+          <t>Non-Oil Exports YoYJAN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -2901,18 +2901,18 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Non-Oil Exports YoYJAN</t>
+          <t>Non-Oil Exports MoMJAN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3044,14 +3044,18 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Capacity Utilization MoMDEC</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -3071,18 +3075,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Industrial Production MoM FinalDEC</t>
+          <t>Capacity Utilization MoMDEC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3102,14 +3102,18 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Industrial Production YoY FinalDEC</t>
+          <t>Industrial Production MoM FinalDEC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -3129,18 +3133,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Industrial Production YoY FinalDEC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3555,17 +3555,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G104" t="n">
         <v>2</v>
       </c>
@@ -3578,21 +3582,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>$-24.0B</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>2</v>
       </c>
@@ -3605,12 +3605,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3655,17 +3655,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G108" t="n">
         <v>2</v>
       </c>
@@ -3678,21 +3682,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
         <v>2</v>
       </c>
@@ -3705,21 +3705,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
         <v>2</v>
       </c>
@@ -3732,17 +3728,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="G111" t="n">
         <v>2</v>
       </c>
@@ -3929,22 +3929,18 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Employment ChangeDEC</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>-130K</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -3991,18 +3987,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Employment ChangeDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-130K</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -4018,14 +4018,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-55.0K</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -4045,14 +4045,18 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Claimant Count ChangeJAN</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-55.0K</t>
+          <t>7.0K</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -4072,18 +4076,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Claimant Count ChangeJAN</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>7.0K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -4103,22 +4103,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -4134,22 +4134,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -4196,22 +4196,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -4227,18 +4227,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4253,23 +4249,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -4280,19 +4276,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BoE Gov Bailey Speech</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>8.1M</t>
+        </is>
+      </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -4303,23 +4303,19 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>BoE Gov Bailey Speech</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>8.1M</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -4330,23 +4326,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4357,23 +4357,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>ZEW Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4384,27 +4388,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -4420,22 +4416,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ZEW Current ConditionsFEB</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -4446,19 +4442,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="G137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -4497,22 +4497,18 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -4528,18 +4524,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -4555,18 +4555,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -4582,18 +4582,18 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -4609,22 +4609,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4666,27 +4666,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -5067,22 +5067,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -5098,18 +5098,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5129,18 +5129,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5160,22 +5160,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -5353,14 +5353,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5380,18 +5384,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5411,18 +5411,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5500,14 +5496,18 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5554,14 +5554,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5639,22 +5639,18 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -5670,18 +5666,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -5724,18 +5724,18 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5812,17 +5812,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G187" t="n">
         <v>3</v>
       </c>
@@ -5835,23 +5839,19 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5867,14 +5867,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -5894,18 +5894,18 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -6202,14 +6202,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -6248,14 +6248,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -6317,18 +6317,18 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -6348,18 +6348,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -6375,22 +6379,18 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6406,14 +6406,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -6510,14 +6510,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -6582,19 +6582,19 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -6609,19 +6609,19 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -6883,22 +6883,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
@@ -6914,22 +6914,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>20K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -6945,14 +6945,18 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>67.1%</t>
+        </is>
+      </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -6972,22 +6976,18 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>67.1%</t>
-        </is>
-      </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
@@ -7003,18 +7003,18 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -7084,16 +7084,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
         <v>3</v>
       </c>
@@ -7111,12 +7107,16 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G237" t="n">
         <v>3</v>
       </c>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>5-Year Bonos Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>8-Year Obligacion Auction</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>8-Year Obligacion Auction</t>
+          <t>5-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -7310,21 +7310,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
       <c r="G245" t="n">
         <v>3</v>
       </c>
@@ -7342,7 +7338,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>3-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -7365,7 +7361,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>3-Year OAT Auction</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7383,17 +7379,21 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G248" t="n">
         <v>3</v>
       </c>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7429,17 +7429,21 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
       <c r="G250" t="n">
         <v>3</v>
       </c>
@@ -7452,19 +7456,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -7475,21 +7487,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
+      <c r="F252" t="inlineStr"/>
       <c r="G252" t="n">
         <v>3</v>
       </c>
@@ -7502,27 +7510,19 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7611,14 +7611,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -7638,12 +7638,16 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G258" t="n">
         <v>3</v>
       </c>
@@ -7661,7 +7665,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -7684,12 +7688,16 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G260" t="n">
         <v>3</v>
       </c>
@@ -7707,7 +7715,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -7725,17 +7733,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="G262" t="n">
         <v>3</v>
       </c>
@@ -7753,16 +7765,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
         <v>3</v>
       </c>
@@ -7780,16 +7788,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
         <v>3</v>
       </c>
@@ -7807,22 +7811,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266">
@@ -7838,18 +7834,18 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -7864,19 +7860,23 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -7896,18 +7896,18 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -7923,18 +7923,18 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7950,14 +7950,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -7977,18 +7977,18 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -8004,14 +8004,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -8076,19 +8076,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Monetary Policy Meeting Minutes</t>
+          <t>Consumer Confidence FlashFEB</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-14</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-14.4</t>
+        </is>
+      </c>
       <c r="G275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -8099,25 +8107,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Monetary Policy Meeting Minutes</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
         <v>3</v>
       </c>
@@ -8130,27 +8130,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Consumer Confidence FlashFEB</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>-14.4</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -8552,12 +8552,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -8648,12 +8648,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -8749,18 +8749,18 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -8771,21 +8771,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>2</v>
       </c>
@@ -8803,18 +8799,18 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8825,17 +8821,21 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
       <c r="G306" t="n">
         <v>2</v>
       </c>
@@ -8880,18 +8880,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -8907,22 +8907,18 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -8938,18 +8934,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8965,18 +8965,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -9023,18 +9023,18 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -9081,18 +9081,18 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -9239,14 +9239,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9266,22 +9266,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>£20.5B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -9324,22 +9324,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>£20.5B</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -9355,18 +9355,18 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326">
@@ -9382,18 +9382,18 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -9432,18 +9432,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -9463,14 +9459,18 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -9605,27 +9605,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -9636,27 +9636,27 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -9667,23 +9667,19 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -9698,23 +9694,23 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -9734,22 +9730,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339">
@@ -9760,19 +9756,23 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -9787,27 +9787,27 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -9823,18 +9823,18 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -9854,22 +9854,18 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr">
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="G342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -9885,18 +9881,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9958,18 +9958,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
@@ -10016,22 +10020,18 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -10047,14 +10047,14 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -10294,22 +10294,18 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G358" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -10325,22 +10321,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G359" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -10356,22 +10352,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361">
@@ -10387,22 +10383,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G361" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -10418,18 +10414,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -10445,22 +10445,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -10665,17 +10665,21 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="G372" t="n">
         <v>3</v>
       </c>
@@ -10688,21 +10692,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+      <c r="F373" t="inlineStr"/>
       <c r="G373" t="n">
         <v>3</v>
       </c>
@@ -10720,14 +10720,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -10747,14 +10747,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G375" t="n">
@@ -10774,14 +10774,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -10797,14 +10797,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378">
@@ -10901,22 +10901,22 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -10932,22 +10932,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -10963,18 +10963,18 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G383" t="n">
@@ -10994,18 +10994,18 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G384" t="n">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -11539,14 +11539,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G407" t="n">
@@ -11566,14 +11566,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G408" t="n">
@@ -11588,25 +11588,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
         <v>2</v>
       </c>
@@ -11650,23 +11642,27 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
-      <c r="E411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -11677,19 +11673,23 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -11796,19 +11796,19 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>CBI Distributive TradesFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -11823,19 +11823,19 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>CBI Distributive TradesFEB</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>-26</t>
         </is>
       </c>
       <c r="G418" t="n">
@@ -11915,6 +11915,198 @@
         <v>3</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Manufacturing Sales MoM PrelJAN</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:25:00+05:30</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Redbook YoYFEB/22</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="G425" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G429"/>
+  <dimension ref="A1:G435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,26 +1323,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1428,26 +1428,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1773,18 +1773,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1804,22 +1804,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1830,23 +1834,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1866,26 +1874,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1901,12 +1909,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1916,7 +1924,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1931,23 +1939,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -1967,12 +1975,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1982,7 +1990,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2002,26 +2010,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2032,27 +2040,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2067,12 +2071,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2082,16 +2086,16 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -2107,22 +2111,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2173,18 +2173,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2239,26 +2239,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2274,22 +2274,18 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2309,22 +2305,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2575,23 +2575,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2604,19 +2600,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2688,22 +2688,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2750,14 +2750,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -2777,22 +2781,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2808,18 +2812,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -2839,18 +2839,18 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -2959,22 +2959,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>9.95%</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2990,18 +2986,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>6.99%</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3017,13 +3017,13 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -3075,14 +3075,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Capacity Utilization MoMDEC</t>
+          <t>Industrial Production YoY FinalDEC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3133,14 +3133,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Industrial Production YoY FinalDEC</t>
+          <t>Capacity Utilization MoMDEC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3514,12 +3514,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G102" t="n">
         <v>2</v>
       </c>
@@ -3532,17 +3536,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>TRY-150.0B</t>
+        </is>
+      </c>
       <c r="G103" t="n">
         <v>2</v>
       </c>
@@ -3560,16 +3568,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>$-24.0B</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>2</v>
       </c>
@@ -3582,12 +3586,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3605,12 +3609,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3628,21 +3632,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>TRY-150.0B</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>2</v>
       </c>
@@ -3660,14 +3660,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -3733,14 +3733,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -3929,14 +3929,18 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Employment ChangeDEC</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-130K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -3956,22 +3960,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3987,22 +3991,18 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -4076,18 +4076,18 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>Employment ChangeDEC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-130K</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -4103,18 +4103,18 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -4196,18 +4196,18 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -4222,23 +4222,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -4254,18 +4254,18 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>8.1M</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4276,23 +4276,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>BoE Gov Bailey Speech</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>8.1M</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -4308,14 +4304,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BoE Gov Bailey Speech</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -4331,18 +4335,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -4357,27 +4357,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ZEW Current ConditionsFEB</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-89</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -4388,19 +4384,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -4416,22 +4420,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>ZEW Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -4442,23 +4446,19 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
@@ -4497,14 +4497,18 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -4524,18 +4528,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -4555,18 +4555,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -4609,22 +4613,18 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -4671,18 +4671,18 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -4866,19 +4866,19 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4889,19 +4889,19 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
@@ -5036,18 +5036,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -5129,18 +5129,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5249,12 +5249,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>RBA Chart Pack</t>
+          <t>Wage Price Index QoQQ4</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G167" t="n">
         <v>3</v>
       </c>
@@ -5272,20 +5280,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Wage Price Index QoQQ4</t>
+          <t>RBA Chart Pack</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="n">
         <v>3</v>
       </c>
@@ -5353,18 +5353,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5384,14 +5380,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5411,14 +5411,18 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5438,14 +5442,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5465,18 +5469,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5496,18 +5496,18 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5581,18 +5581,18 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5608,18 +5608,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5639,18 +5635,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -5724,18 +5724,18 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5812,21 +5812,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
         <v>3</v>
       </c>
@@ -5839,19 +5835,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5867,14 +5867,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -5894,18 +5894,18 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -5948,18 +5948,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Current Account s.aDEC</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>€30B</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>€30B</t>
+          <t>€32B</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -5979,14 +5975,18 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>Current Account s.aDEC</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>€30B</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>€32B</t>
+          <t>€30B</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -6001,21 +6001,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
         <v>3</v>
       </c>
@@ -6028,17 +6024,21 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G195" t="n">
         <v>3</v>
       </c>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -6202,14 +6202,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -6294,14 +6294,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
@@ -6582,21 +6582,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
         <v>3</v>
       </c>
@@ -6609,21 +6605,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>Annual Budget Speech</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
         <v>3</v>
       </c>
@@ -6636,17 +6628,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual Budget Speech</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6659,17 +6655,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
       <c r="G220" t="n">
         <v>3</v>
       </c>
@@ -6883,22 +6883,18 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>20K</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
@@ -6976,14 +6972,18 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>20K</t>
+        </is>
+      </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -7003,18 +7003,18 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -7129,19 +7129,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -7187,19 +7187,19 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>5-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>8-Year Obligacion Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>5-Year Bonos Auction</t>
+          <t>8-Year Obligacion Auction</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -7333,17 +7333,21 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G246" t="n">
         <v>3</v>
       </c>
@@ -7379,21 +7383,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
       <c r="G248" t="n">
         <v>3</v>
       </c>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7429,21 +7429,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
+      <c r="F250" t="inlineStr"/>
       <c r="G250" t="n">
         <v>3</v>
       </c>
@@ -7456,27 +7452,23 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7487,19 +7479,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
       <c r="G252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7611,14 +7611,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -7638,14 +7638,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -7688,14 +7688,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -7715,14 +7715,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G261" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -7733,21 +7741,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="F262" t="inlineStr"/>
       <c r="G262" t="n">
         <v>3</v>
       </c>
@@ -7860,27 +7864,23 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
@@ -7896,18 +7896,18 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -7950,18 +7950,18 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -8004,14 +8004,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -8598,21 +8598,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
         <v>3</v>
       </c>
@@ -8625,17 +8621,21 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G298" t="n">
         <v>3</v>
       </c>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -8880,18 +8880,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -8907,14 +8907,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -8965,18 +8965,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -9023,18 +9023,18 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -9050,18 +9050,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9081,18 +9077,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -9158,14 +9158,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>HSBC Manufacturing PMI FlashFEB</t>
+          <t>HSBC Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -9185,14 +9185,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HSBC Services PMI FlashFEB</t>
+          <t>HSBC Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -9212,14 +9212,18 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -9266,22 +9270,18 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
@@ -9297,18 +9297,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -9324,22 +9328,18 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
@@ -9355,18 +9355,18 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -9382,18 +9382,18 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -9521,22 +9521,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -9552,18 +9552,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -9583,18 +9579,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -9641,18 +9641,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -9667,23 +9663,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337">
@@ -9730,18 +9730,18 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -9756,23 +9756,23 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -9823,18 +9823,18 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -9854,18 +9854,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F342" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -9881,22 +9885,18 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -10352,18 +10352,18 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -10414,22 +10414,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -10445,22 +10445,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -10670,14 +10670,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -10692,17 +10692,21 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="G373" t="n">
         <v>3</v>
       </c>
@@ -10720,14 +10724,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -10742,21 +10746,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
+      <c r="F375" t="inlineStr"/>
       <c r="G375" t="n">
         <v>3</v>
       </c>
@@ -10901,22 +10901,22 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -10932,18 +10932,18 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G382" t="n">
@@ -10963,22 +10963,22 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -11539,14 +11539,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G407" t="n">
@@ -11566,14 +11566,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G408" t="n">
@@ -11796,19 +11796,19 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>CBI Distributive TradesFEB</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>-26</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -11823,19 +11823,19 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>CBI Distributive TradesFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G418" t="n">
@@ -11850,17 +11850,21 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI YoYFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G419" t="n">
         <v>3</v>
       </c>
@@ -11896,21 +11900,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>IPCA mid-month CPI YoYFEB</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F421" t="inlineStr"/>
       <c r="G421" t="n">
         <v>3</v>
       </c>
@@ -11997,18 +11997,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="F425" t="inlineStr"/>
       <c r="G425" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="426">
@@ -12024,7 +12020,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -12042,17 +12038,21 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G427" t="n">
         <v>3</v>
       </c>
@@ -12070,14 +12070,18 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="G428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -12088,22 +12092,164 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr">
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Current AccountQ4</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>$ 7500M</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
         <is>
           <t>5.1%</t>
         </is>
       </c>
-      <c r="G429" t="n">
+      <c r="G435" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G435"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,26 +1323,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1393,26 +1393,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1428,22 +1428,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1773,22 +1773,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1799,12 +1803,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1814,16 +1818,16 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -1834,27 +1838,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1874,26 +1874,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1944,18 +1944,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2010,26 +2010,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2040,23 +2040,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2076,22 +2080,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2106,23 +2106,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2173,22 +2173,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2204,22 +2208,18 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2274,18 +2274,18 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2305,26 +2305,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2575,19 +2575,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2658,19 +2658,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2688,22 +2688,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2719,18 +2719,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -2750,13 +2750,13 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2781,22 +2781,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2850,11 +2850,11 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2870,18 +2870,18 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Non-Oil Exports YoYJAN</t>
+          <t>Non-Oil Exports MoMJAN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -2901,18 +2901,18 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Non-Oil Exports MoMJAN</t>
+          <t>Non-Oil Exports YoYJAN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -2959,18 +2959,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>9.95%</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2986,22 +2990,18 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>9.95%</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3187,14 +3187,10 @@
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>€4.35B</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>€4.5B</t>
+          <t>€ -4.9B</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -3209,7 +3205,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3218,10 +3214,14 @@
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>€4.35B</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>€ -4.9B</t>
+          <t>€4.5B</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -3372,15 +3372,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Foreign Securities PurchasesDEC</t>
+          <t>Foreign Securities Purchases by CanadiansDEC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>C$14.23B</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>3</v>
@@ -3399,11 +3395,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Foreign Securities Purchases by CanadiansDEC</t>
+          <t>Foreign Securities PurchasesDEC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>C$14.23B</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>3</v>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3509,19 +3509,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>$-24.0B</t>
+          <t>TRY-150.0B</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -3536,21 +3536,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>TRY-150.0B</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>2</v>
       </c>
@@ -3637,12 +3633,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G107" t="n">
         <v>2</v>
       </c>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3929,22 +3929,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Claimant Count ChangeJAN</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.0K</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -3960,22 +3960,18 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>-55.0K</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -4018,18 +4014,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-55.0K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -4045,22 +4045,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Claimant Count ChangeJAN</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>7.0K</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -4103,22 +4103,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -4134,22 +4134,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -4222,21 +4222,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>BoE Gov Bailey Speech</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>32.4%</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
         <v>2</v>
       </c>
@@ -4249,19 +4245,19 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>8.1M</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4281,14 +4277,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BoE Gov Bailey Speech</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -4299,27 +4303,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -4330,19 +4330,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>8.1M</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -4357,23 +4357,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4389,22 +4385,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>ZEW Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -4420,22 +4416,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ZEW Current ConditionsFEB</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -4446,19 +4442,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="G137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -4497,22 +4497,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -4555,18 +4555,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -4586,18 +4582,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -4608,23 +4608,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4635,27 +4639,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4671,22 +4675,18 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4912,12 +4912,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -5036,22 +5036,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -5067,22 +5067,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -5098,18 +5098,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5129,18 +5129,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5160,22 +5160,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -5380,18 +5380,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5411,18 +5411,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
         <is>
           <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5442,14 +5438,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5469,14 +5465,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5496,18 +5496,18 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5724,22 +5724,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Interest Rate Decision</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -5755,22 +5755,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Interest Rate Decision</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5948,14 +5948,18 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>Current Account s.aDEC</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>€30B</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>€32B</t>
+          <t>€30B</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -5975,18 +5979,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Current Account s.aDEC</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>€30B</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>€30B</t>
+          <t>€32B</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -6001,17 +6001,21 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G194" t="n">
         <v>3</v>
       </c>
@@ -6024,21 +6028,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F195" t="inlineStr"/>
       <c r="G195" t="n">
         <v>3</v>
       </c>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -6106,14 +6106,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -6317,22 +6317,18 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -6348,22 +6344,18 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -6379,18 +6371,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -6406,18 +6402,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -6510,14 +6510,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -6582,17 +6582,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="G217" t="n">
         <v>3</v>
       </c>
@@ -6605,12 +6609,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual Budget Speech</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -6628,21 +6632,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Annual Budget Speech</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6710,18 +6710,18 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223">
@@ -6764,18 +6764,18 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -6883,18 +6883,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>20K</t>
+        </is>
+      </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
@@ -6910,22 +6914,18 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231">
@@ -6972,22 +6972,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>20K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -7084,12 +7084,16 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G236" t="n">
         <v>3</v>
       </c>
@@ -7107,16 +7111,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
+      <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
         <v>3</v>
       </c>
@@ -7129,19 +7129,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -7187,19 +7187,19 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>5-Year Bonos Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>5-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -7333,21 +7333,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
         <v>3</v>
       </c>
@@ -7383,17 +7379,21 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G248" t="n">
         <v>3</v>
       </c>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -7452,21 +7452,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
       <c r="G251" t="n">
         <v>3</v>
       </c>
@@ -7479,27 +7475,23 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7510,19 +7502,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7611,14 +7611,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -7638,14 +7638,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -7665,12 +7665,16 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G259" t="n">
         <v>3</v>
       </c>
@@ -7683,19 +7687,19 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -7715,22 +7719,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
       <c r="G261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262">
@@ -7864,23 +7860,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -7950,18 +7950,18 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8004,18 +8004,18 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -8076,27 +8076,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Consumer Confidence FlashFEB</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>-14.4</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -8130,27 +8130,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Consumer Confidence FlashFEB</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-14.4</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -8442,14 +8442,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8648,12 +8648,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -8744,21 +8744,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
         <v>2</v>
       </c>
@@ -8771,19 +8767,23 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
       <c r="G304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -8799,18 +8799,18 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8826,14 +8826,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -9131,14 +9131,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -9185,14 +9185,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HSBC Manufacturing PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -9212,22 +9212,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>£20.5B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -9243,18 +9243,18 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -9270,14 +9270,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9297,22 +9297,18 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
@@ -9328,18 +9324,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -9610,18 +9610,18 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -9641,14 +9641,18 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -9663,27 +9667,23 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -9699,22 +9699,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338">
@@ -9756,23 +9756,23 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -9792,18 +9792,18 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -9912,14 +9912,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Monetary Policy Meeting Minutes</t>
+          <t>Foreign Exchange ReservesFEB/14</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
       <c r="G344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9935,14 +9935,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/14</t>
+          <t>Monetary Policy Meeting Minutes</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr"/>
       <c r="G345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -10074,18 +10074,18 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G350" t="n">
@@ -10105,18 +10105,18 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Retail Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -10294,14 +10294,18 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -10321,22 +10325,18 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
@@ -10352,22 +10352,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
@@ -10383,18 +10383,18 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -10414,22 +10414,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -10445,18 +10445,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -10476,18 +10476,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -10548,21 +10548,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F367" t="inlineStr"/>
       <c r="G367" t="n">
         <v>3</v>
       </c>
@@ -10575,12 +10571,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -10598,17 +10594,21 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G369" t="n">
         <v>3</v>
       </c>
@@ -10621,12 +10621,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10670,14 +10670,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -10697,14 +10697,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -10719,21 +10719,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+      <c r="F374" t="inlineStr"/>
       <c r="G374" t="n">
         <v>3</v>
       </c>
@@ -10746,17 +10742,21 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
       <c r="G375" t="n">
         <v>3</v>
       </c>
@@ -10774,14 +10774,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377">
@@ -10797,14 +10797,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -10820,18 +10820,18 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -10847,18 +10847,18 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -10874,14 +10874,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -10932,22 +10932,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -10963,22 +10963,22 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -10994,18 +10994,18 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G384" t="n">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -11539,14 +11539,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G407" t="n">
@@ -11566,14 +11566,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G408" t="n">
@@ -11588,19 +11588,23 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -11616,7 +11620,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -11647,7 +11651,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -11673,23 +11677,19 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -11850,21 +11850,17 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>IPCA mid-month CPI YoYFEB</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
         <v>3</v>
       </c>
@@ -11900,17 +11896,21 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI YoYFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G421" t="n">
         <v>3</v>
       </c>
@@ -11969,17 +11969,21 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G424" t="n">
         <v>3</v>
       </c>
@@ -11997,7 +12001,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -12020,14 +12024,18 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="G426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -12038,21 +12046,17 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F427" t="inlineStr"/>
       <c r="G427" t="n">
         <v>3</v>
       </c>
@@ -12070,18 +12074,14 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="F428" t="inlineStr"/>
       <c r="G428" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -12138,21 +12138,17 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>$ 7500M</t>
-        </is>
-      </c>
+      <c r="F431" t="inlineStr"/>
       <c r="G431" t="n">
         <v>3</v>
       </c>
@@ -12170,14 +12166,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -12188,17 +12184,21 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G433" t="n">
         <v>3</v>
       </c>
@@ -12211,17 +12211,21 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>$ 7500M</t>
+        </is>
+      </c>
       <c r="G434" t="n">
         <v>3</v>
       </c>
@@ -12234,22 +12238,91 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr">
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr">
         <is>
           <t>5.1%</t>
         </is>
       </c>
-      <c r="G435" t="n">
+      <c r="G438" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G438"/>
+  <dimension ref="A1:G441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1428,26 +1428,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1773,22 +1773,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1803,23 +1799,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1834,27 +1830,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1874,26 +1866,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1909,12 +1901,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1924,7 +1916,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1939,12 +1931,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1954,16 +1946,16 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -1979,12 +1971,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1994,7 +1986,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2014,26 +2006,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2044,23 +2036,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2080,18 +2076,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2111,22 +2107,26 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2208,22 +2208,26 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2239,18 +2243,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2270,26 +2274,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2580,14 +2580,18 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2600,23 +2604,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2634,18 +2634,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2658,19 +2654,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2688,18 +2688,18 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2719,18 +2719,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -2750,13 +2750,13 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2781,22 +2781,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2839,22 +2839,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2959,22 +2959,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>9.95%</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2990,18 +2986,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>9.95%</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3044,18 +3044,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Capacity Utilization MoMDEC</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -3075,14 +3071,18 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Industrial Production YoY FinalDEC</t>
+          <t>Industrial Production MoM FinalDEC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3102,18 +3102,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Industrial Production MoM FinalDEC</t>
+          <t>Industrial Production YoY FinalDEC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -3133,14 +3129,18 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Capacity Utilization MoMDEC</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -3514,14 +3514,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TRY-150.0B</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -3541,12 +3541,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G103" t="n">
         <v>2</v>
       </c>
@@ -3564,7 +3568,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3582,12 +3586,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3605,12 +3609,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3628,21 +3632,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>$-24.0B</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>2</v>
       </c>
@@ -3660,14 +3660,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>TRY-150.0B</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -3682,17 +3682,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G109" t="n">
         <v>2</v>
       </c>
@@ -3705,12 +3709,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -3728,21 +3732,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
         <v>2</v>
       </c>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -4014,18 +4014,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Employment ChangeDEC</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-130K</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -4076,14 +4072,18 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Employment ChangeDEC</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-130K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -4134,18 +4134,18 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -4196,22 +4196,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -4227,14 +4227,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BoE Gov Bailey Speech</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4250,14 +4254,18 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4277,22 +4285,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>BoE Gov Bailey Speech</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -4308,18 +4308,18 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>8.1M</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -4335,18 +4335,18 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>8.1M</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -4357,19 +4357,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -4411,27 +4415,19 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -4442,7 +4438,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4451,14 +4447,18 @@
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -4497,22 +4497,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -4555,14 +4555,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -4582,22 +4586,18 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -4608,27 +4608,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -4639,27 +4635,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4675,18 +4671,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -5036,22 +5036,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -5067,22 +5067,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -5098,18 +5098,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5160,22 +5160,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -5218,18 +5218,18 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wage Price Index YoYQ4</t>
+          <t>Wage Price Index QoQQ4</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -5249,20 +5249,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wage Price Index QoQQ4</t>
+          <t>RBA Chart Pack</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
         <v>3</v>
       </c>
@@ -5280,12 +5272,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>RBA Chart Pack</t>
+          <t>Wage Price Index YoYQ4</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="G168" t="n">
         <v>3</v>
       </c>
@@ -5353,18 +5353,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -5380,18 +5384,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
         <is>
           <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5411,14 +5411,18 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5438,14 +5442,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5465,18 +5469,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5496,18 +5500,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5527,14 +5527,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -5554,14 +5554,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5581,18 +5581,18 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -5608,18 +5608,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -5635,22 +5639,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -5666,22 +5670,18 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5724,22 +5724,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Interest Rate Decision</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -5755,22 +5755,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Interest Rate Decision</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5812,19 +5812,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5862,23 +5866,19 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -5948,18 +5948,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Current Account s.aDEC</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>€30B</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>€30B</t>
+          <t>€32B</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -5979,14 +5975,18 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>Current Account s.aDEC</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>€30B</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>€32B</t>
+          <t>€30B</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -6001,21 +6001,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
         <v>3</v>
       </c>
@@ -6028,17 +6024,21 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G195" t="n">
         <v>3</v>
       </c>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -6106,14 +6106,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -6202,14 +6202,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -6294,14 +6294,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -6317,18 +6317,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -6344,14 +6348,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -6371,22 +6375,18 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -6510,14 +6510,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Stock Investment by ForeignersFEB/15</t>
+          <t>Foreign Bond InvestmentFEB/15</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentFEB/15</t>
+          <t>Stock Investment by ForeignersFEB/15</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -6883,22 +6883,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>20K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -6914,18 +6914,18 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
@@ -6941,18 +6941,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>67.1%</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -6972,22 +6968,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233">
@@ -7003,14 +6999,18 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>20K</t>
+        </is>
+      </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -7129,19 +7129,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -7161,22 +7161,18 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -7187,23 +7183,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>8-Year Obligacion Auction</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>5-Year Bonos Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>8-Year Obligacion Auction</t>
+          <t>5-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -7502,27 +7502,19 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7533,19 +7525,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -7638,18 +7638,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259">
@@ -7665,14 +7669,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -7719,12 +7723,16 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G261" t="n">
         <v>3</v>
       </c>
@@ -7742,7 +7750,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -7765,7 +7773,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -7788,7 +7796,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -7811,7 +7819,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7834,22 +7842,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
@@ -7896,14 +7896,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -7923,18 +7923,18 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7950,14 +7950,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8004,18 +8004,18 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -8460,19 +8460,19 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>2-Year Bond Auction</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -8483,19 +8483,19 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2-Year Bond Auction</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -8744,19 +8744,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
       <c r="G303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -8772,18 +8776,18 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -8821,21 +8825,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
         <v>2</v>
       </c>
@@ -8907,14 +8907,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -8934,22 +8934,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8965,18 +8961,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -9023,18 +9023,18 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -9050,14 +9050,18 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9077,22 +9081,18 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -9212,22 +9212,18 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -9243,18 +9239,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -9270,14 +9270,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9297,14 +9297,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -9324,22 +9324,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>£20.5B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -9355,18 +9355,18 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326">
@@ -9382,18 +9382,18 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -9432,14 +9432,18 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -9490,18 +9494,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -9521,18 +9521,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -9552,18 +9548,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -9579,22 +9579,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -9605,23 +9605,23 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -9636,23 +9636,23 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -9667,23 +9667,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337">
@@ -9725,27 +9729,27 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
@@ -9756,23 +9760,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -9787,23 +9787,23 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -9912,14 +9912,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/14</t>
+          <t>Monetary Policy Meeting Minutes</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
       <c r="G344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9935,14 +9935,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Monetary Policy Meeting Minutes</t>
+          <t>Foreign Exchange ReservesFEB/14</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr"/>
       <c r="G345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -10105,18 +10105,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales MoM PrelJAN</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -10136,18 +10132,18 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Retail Sales MoM PrelJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G352" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="353">
@@ -10163,18 +10159,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G353" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -10325,18 +10325,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G359" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360">
@@ -10352,22 +10356,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361">
@@ -10383,18 +10387,18 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -10414,22 +10418,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363">
@@ -10445,22 +10449,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -10476,18 +10476,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -10571,17 +10571,21 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G368" t="n">
         <v>3</v>
       </c>
@@ -10594,21 +10598,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F369" t="inlineStr"/>
       <c r="G369" t="n">
         <v>3</v>
       </c>
@@ -10621,12 +10621,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10665,21 +10665,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="F372" t="inlineStr"/>
       <c r="G372" t="n">
         <v>3</v>
       </c>
@@ -10719,17 +10715,21 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
       <c r="G374" t="n">
         <v>3</v>
       </c>
@@ -10747,14 +10747,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G375" t="n">
@@ -10774,14 +10774,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -10797,14 +10797,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378">
@@ -10847,18 +10847,18 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -10874,18 +10874,18 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -10932,22 +10932,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -10994,22 +10994,22 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>9-Month Bubill Auction</t>
+          <t>3-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>3-Month Bubill Auction</t>
+          <t>9-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -11438,12 +11438,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>20-Year KTB Auction</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -11484,12 +11484,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>20-Year KTB Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -11512,14 +11512,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G406" t="n">
@@ -11539,14 +11539,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G407" t="n">
@@ -11646,25 +11646,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
       <c r="G411" t="n">
         <v>2</v>
       </c>
@@ -11677,17 +11669,25 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="G412" t="n">
         <v>2</v>
       </c>
@@ -11700,17 +11700,21 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G413" t="n">
         <v>3</v>
       </c>
@@ -11723,21 +11727,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>3</v>
       </c>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -11796,19 +11796,19 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>CBI Distributive TradesFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -11823,19 +11823,19 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>CBI Distributive TradesFEB</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>-26</t>
         </is>
       </c>
       <c r="G418" t="n">
@@ -11873,17 +11873,21 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI MoMFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G420" t="n">
         <v>3</v>
       </c>
@@ -11896,21 +11900,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>IPCA mid-month CPI MoMFEB</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F421" t="inlineStr"/>
       <c r="G421" t="n">
         <v>3</v>
       </c>
@@ -11969,21 +11969,17 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F424" t="inlineStr"/>
       <c r="G424" t="n">
         <v>3</v>
       </c>
@@ -12001,7 +11997,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -12051,7 +12047,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -12069,17 +12065,21 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G428" t="n">
         <v>3</v>
       </c>
@@ -12115,17 +12115,21 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>$ 7500M</t>
+        </is>
+      </c>
       <c r="G430" t="n">
         <v>3</v>
       </c>
@@ -12143,7 +12147,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -12166,14 +12170,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -12184,21 +12188,17 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F433" t="inlineStr"/>
       <c r="G433" t="n">
         <v>3</v>
       </c>
@@ -12211,19 +12211,19 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr">
         <is>
-          <t>$ 7500M</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G434" t="n">
@@ -12243,14 +12243,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -12326,6 +12326,79 @@
         <v>3</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Money SupplyJAN</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>5-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G441" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
